--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6022-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6022-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E26200E7-E954-42A9-8B33-3F5653060163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51D0DFBA-9503-44C7-AD9D-F8623B1D33FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D235525F-EF0A-4B24-8F9D-6C766D975C4E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{585CC2B1-9BD3-4315-A0E6-B20954B922BF}"/>
   </bookViews>
   <sheets>
     <sheet name="6022-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1439,27 +1439,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED61115-CD4F-46DE-8F83-E6CD025A45EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1192476-4397-4A36-AD77-08853E8BD06C}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1493,7 +1492,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1529,7 +1528,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1581,7 +1580,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1649,7 +1648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2016</v>
       </c>
@@ -1721,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2015</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2014</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2013</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2012</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2011</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2010</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2009</v>
       </c>
@@ -2225,7 +2224,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2008</v>
       </c>
@@ -2297,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2007</v>
       </c>
@@ -2369,7 +2368,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2006</v>
       </c>
@@ -2441,7 +2440,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2005</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2004</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2003</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2002</v>
       </c>
@@ -2729,7 +2728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2001</v>
       </c>
@@ -2801,7 +2800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2000</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>1999</v>
       </c>
@@ -2945,7 +2944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>39</v>
       </c>
